--- a/public/templates/pr_meal_template.xlsx
+++ b/public/templates/pr_meal_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OCD CARAGA\Desktop\caraga-supply\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11AD2BB8-D9BB-4724-A5D0-067518001D17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0273186F-FECC-49FE-A3B8-B67DAA60CF34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4305" yWindow="3525" windowWidth="21660" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="meal" sheetId="8" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>PURCHASE REQUEST</t>
   </si>
@@ -340,40 +340,140 @@
     <t>{{block_title}}</t>
   </si>
   <si>
-    <t>{{delivery_site}}</t>
-  </si>
-  <si>
-    <t>{{delivery_period}}</t>
-  </si>
-  <si>
     <t>{{user_name}}</t>
   </si>
   <si>
     <t>{{user_designation}}</t>
   </si>
   <si>
-    <t>{{b_column}}</t>
-  </si>
-  <si>
-    <t>{{c_column}}</t>
-  </si>
-  <si>
-    <t>{{d_column}}</t>
-  </si>
-  <si>
     <t>{{overall_total}}</t>
   </si>
   <si>
-    <t xml:space="preserve">Chargeability: </t>
-  </si>
-  <si>
     <t xml:space="preserve">PR No.  :{{pr_number}} </t>
   </si>
   <si>
-    <t>{{f_column}}</t>
-  </si>
-  <si>
-    <t>{{g_column}}</t>
+    <r>
+      <t xml:space="preserve">Chargeability: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>{{chargeability}}</t>
+    </r>
+  </si>
+  <si>
+    <t>No. of Pax</t>
+  </si>
+  <si>
+    <t>Meal / Snack</t>
+  </si>
+  <si>
+    <t>Serving Arrangement</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>Other requirements/
+Remarks</t>
+  </si>
+  <si>
+    <t>Room Requirement</t>
+  </si>
+  <si>
+    <t>No. of Rooms</t>
+  </si>
+  <si>
+    <t>Check-In Date/Time</t>
+  </si>
+  <si>
+    <t>Check-Out Date/Time</t>
+  </si>
+  <si>
+    <t>No. of Nights</t>
+  </si>
+  <si>
+    <t>Other requirements</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delivery Site:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> {{delivery_site}}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Delivery Period:</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> {{delivery_period}}</t>
+    </r>
+  </si>
+  <si>
+    <t>Location: {{delivery_site}}</t>
+  </si>
+  <si>
+    <r>
+      <t>Date:</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>{{delivery_period}}</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -384,7 +484,7 @@
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -480,12 +580,6 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -501,7 +595,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -741,13 +835,65 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -758,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
@@ -873,9 +1019,6 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -886,9 +1029,6 @@
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -928,9 +1068,6 @@
     </xf>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -963,10 +1100,59 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -998,6 +1184,21 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1019,12 +1220,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1034,11 +1253,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1069,21 +1288,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1303,172 +1510,179 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L902"/>
+  <dimension ref="A1:M907"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="78" customWidth="1"/>
-    <col min="2" max="2" width="15.28515625" style="78" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" style="78" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="78" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" style="78" customWidth="1"/>
-    <col min="6" max="6" width="32.140625" style="78" customWidth="1"/>
-    <col min="7" max="7" width="35" style="78" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="78" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" style="78" customWidth="1"/>
-    <col min="10" max="10" width="17" style="78" customWidth="1"/>
-    <col min="11" max="11" width="4.85546875" style="78" customWidth="1"/>
-    <col min="12" max="12" width="23.5703125" style="78" customWidth="1"/>
-    <col min="13" max="25" width="8.7109375" style="78" customWidth="1"/>
-    <col min="26" max="16384" width="14.42578125" style="78"/>
+    <col min="1" max="1" width="16.140625" style="75" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="75" customWidth="1"/>
+    <col min="3" max="3" width="23.85546875" style="75" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="75" customWidth="1"/>
+    <col min="5" max="8" width="26.85546875" style="75" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="75" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" style="75" customWidth="1"/>
+    <col min="11" max="11" width="17" style="75" customWidth="1"/>
+    <col min="12" max="12" width="4.85546875" style="75" customWidth="1"/>
+    <col min="13" max="13" width="23.5703125" style="75" customWidth="1"/>
+    <col min="14" max="26" width="8.7109375" style="75" customWidth="1"/>
+    <col min="27" max="16384" width="14.42578125" style="75"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="123" t="s">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="124"/>
-      <c r="C1" s="124"/>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="125"/>
-    </row>
-    <row r="2" spans="1:12" ht="23.25" x14ac:dyDescent="0.35">
-      <c r="A2" s="126" t="s">
+      <c r="B1" s="151"/>
+      <c r="C1" s="151"/>
+      <c r="D1" s="151"/>
+      <c r="E1" s="151"/>
+      <c r="F1" s="151"/>
+      <c r="G1" s="151"/>
+      <c r="H1" s="151"/>
+      <c r="I1" s="151"/>
+      <c r="J1" s="151"/>
+      <c r="K1" s="151"/>
+      <c r="L1" s="151"/>
+      <c r="M1" s="152"/>
+    </row>
+    <row r="2" spans="1:13" ht="23.25" x14ac:dyDescent="0.35">
+      <c r="A2" s="153" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="127"/>
-      <c r="C2" s="127"/>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="127"/>
-      <c r="K2" s="127"/>
-      <c r="L2" s="128"/>
-    </row>
-    <row r="3" spans="1:12" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="129" t="s">
+      <c r="B2" s="154"/>
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="154"/>
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="155"/>
+    </row>
+    <row r="3" spans="1:13" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="156" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="130"/>
-      <c r="C3" s="130"/>
-      <c r="D3" s="130"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="131"/>
-    </row>
-    <row r="4" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="132" t="s">
+      <c r="B3" s="157"/>
+      <c r="C3" s="157"/>
+      <c r="D3" s="157"/>
+      <c r="E3" s="157"/>
+      <c r="F3" s="157"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="157"/>
+      <c r="M3" s="158"/>
+    </row>
+    <row r="4" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="159" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="133"/>
-      <c r="D4" s="133"/>
-      <c r="E4" s="133"/>
-      <c r="F4" s="133"/>
-      <c r="G4" s="133"/>
-      <c r="H4" s="133"/>
-      <c r="I4" s="133"/>
-      <c r="J4" s="133"/>
-      <c r="K4" s="133"/>
-      <c r="L4" s="134"/>
-    </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="135" t="s">
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="161"/>
+    </row>
+    <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="162" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="136"/>
-      <c r="J5" s="136"/>
-      <c r="K5" s="136"/>
-      <c r="L5" s="137"/>
-    </row>
-    <row r="6" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="135" t="s">
+      <c r="B5" s="163"/>
+      <c r="C5" s="163"/>
+      <c r="D5" s="163"/>
+      <c r="E5" s="163"/>
+      <c r="F5" s="163"/>
+      <c r="G5" s="163"/>
+      <c r="H5" s="163"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="163"/>
+      <c r="K5" s="163"/>
+      <c r="L5" s="163"/>
+      <c r="M5" s="164"/>
+    </row>
+    <row r="6" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="162" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="136"/>
-      <c r="C6" s="136"/>
-      <c r="D6" s="136"/>
-      <c r="E6" s="136"/>
-      <c r="F6" s="136"/>
-      <c r="G6" s="136"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="136"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="136"/>
-      <c r="L6" s="137"/>
-    </row>
-    <row r="7" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="135" t="s">
+      <c r="B6" s="163"/>
+      <c r="C6" s="163"/>
+      <c r="D6" s="163"/>
+      <c r="E6" s="163"/>
+      <c r="F6" s="163"/>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="163"/>
+      <c r="K6" s="163"/>
+      <c r="L6" s="163"/>
+      <c r="M6" s="164"/>
+    </row>
+    <row r="7" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="162" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="136"/>
-      <c r="C7" s="136"/>
-      <c r="D7" s="136"/>
-      <c r="E7" s="136"/>
-      <c r="F7" s="136"/>
-      <c r="G7" s="136"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="136"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="137"/>
-    </row>
-    <row r="8" spans="1:12" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="135" t="s">
+      <c r="B7" s="163"/>
+      <c r="C7" s="163"/>
+      <c r="D7" s="163"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="163"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="163"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="163"/>
+      <c r="K7" s="163"/>
+      <c r="L7" s="163"/>
+      <c r="M7" s="164"/>
+    </row>
+    <row r="8" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="162" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="136"/>
-      <c r="C8" s="136"/>
-      <c r="D8" s="136"/>
-      <c r="E8" s="136"/>
-      <c r="F8" s="136"/>
-      <c r="G8" s="136"/>
-      <c r="H8" s="136"/>
-      <c r="I8" s="136"/>
-      <c r="J8" s="136"/>
-      <c r="K8" s="136"/>
-      <c r="L8" s="137"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="163"/>
+      <c r="C8" s="163"/>
+      <c r="D8" s="163"/>
+      <c r="E8" s="163"/>
+      <c r="F8" s="163"/>
+      <c r="G8" s="163"/>
+      <c r="H8" s="163"/>
+      <c r="I8" s="163"/>
+      <c r="J8" s="163"/>
+      <c r="K8" s="163"/>
+      <c r="L8" s="163"/>
+      <c r="M8" s="164"/>
+    </row>
+    <row r="9" spans="1:13" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
+      <c r="G9" s="3"/>
       <c r="H9" s="4"/>
-      <c r="I9" s="66" t="s">
-        <v>76</v>
-      </c>
-      <c r="J9" s="67"/>
-      <c r="K9" s="66"/>
-      <c r="L9" s="68" t="s">
+      <c r="I9" s="4"/>
+      <c r="J9" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="K9" s="65"/>
+      <c r="L9" s="64"/>
+      <c r="M9" s="66" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>6</v>
       </c>
@@ -1480,16 +1694,17 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="1" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="69"/>
-      <c r="L10" s="70" t="s">
+      <c r="K10" s="67"/>
+      <c r="M10" s="68" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" s="1" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>10</v>
       </c>
@@ -1500,980 +1715,1129 @@
       <c r="D11" s="10"/>
       <c r="E11" s="10"/>
       <c r="F11" s="10"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="71" t="s">
+      <c r="G11" s="10"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="72"/>
-      <c r="K11" s="71"/>
-      <c r="L11" s="73" t="s">
+      <c r="K11" s="70"/>
+      <c r="L11" s="69"/>
+      <c r="M11" s="71" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" s="1" customFormat="1" ht="40.5" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="141" t="s">
+      <c r="B12" s="166" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="100"/>
-      <c r="D12" s="100"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="100"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="34" t="s">
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="116"/>
+      <c r="G12" s="116"/>
+      <c r="H12" s="117"/>
+      <c r="I12" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="I12" s="34" t="s">
+      <c r="J12" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="J12" s="35" t="s">
+      <c r="K12" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="K12" s="141" t="s">
+      <c r="L12" s="166" t="s">
         <v>17</v>
       </c>
-      <c r="L12" s="101"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="M12" s="117"/>
+    </row>
+    <row r="13" spans="1:13" s="1" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
-      <c r="B13" s="138" t="s">
+      <c r="B13" s="105" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="92"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="37"/>
-      <c r="K13" s="36"/>
-      <c r="L13" s="38"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
+      <c r="G13" s="99"/>
+      <c r="H13" s="108"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="38"/>
+    </row>
+    <row r="14" spans="1:13" s="1" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6"/>
-      <c r="B14" s="139"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="37"/>
-      <c r="K14" s="36"/>
-      <c r="L14" s="39"/>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="165"/>
+      <c r="C14" s="99"/>
+      <c r="D14" s="99"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
+      <c r="G14" s="99"/>
+      <c r="H14" s="108"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
+      <c r="L14" s="36"/>
+      <c r="M14" s="39"/>
+    </row>
+    <row r="15" spans="1:13" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6"/>
-      <c r="B15" s="138" t="s">
+      <c r="B15" s="105" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="91"/>
-      <c r="D15" s="91"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="39" t="s">
+      <c r="C15" s="99"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="99"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="99"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="36"/>
+      <c r="M15" s="39" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:12" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" s="1" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6"/>
-      <c r="B16" s="140" t="s">
-        <v>67</v>
-      </c>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="91"/>
-      <c r="G16" s="92"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="36"/>
-      <c r="L16" s="39"/>
-    </row>
-    <row r="17" spans="1:12" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="98" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="99"/>
+      <c r="D16" s="99"/>
+      <c r="E16" s="99"/>
+      <c r="F16" s="99"/>
+      <c r="G16" s="99"/>
+      <c r="H16" s="108"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="37"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="39"/>
+    </row>
+    <row r="17" spans="1:13" s="1" customFormat="1" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6"/>
-      <c r="B17" s="140" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="91"/>
-      <c r="D17" s="91"/>
-      <c r="E17" s="91"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="39"/>
-    </row>
-    <row r="18" spans="1:12" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="98" t="s">
+        <v>84</v>
+      </c>
+      <c r="C17" s="99"/>
+      <c r="D17" s="99"/>
+      <c r="E17" s="99"/>
+      <c r="F17" s="99"/>
+      <c r="G17" s="99"/>
+      <c r="H17" s="99"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="36"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="39"/>
+    </row>
+    <row r="18" spans="1:13" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6"/>
-      <c r="B18" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="58" t="s">
+      <c r="B18" s="56" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="C18" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="D18" s="56" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="F18" s="89" t="s">
+      <c r="F18" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="101" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="102"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="93"/>
+      <c r="K18" s="51"/>
+      <c r="L18" s="50"/>
+      <c r="M18" s="52"/>
+    </row>
+    <row r="19" spans="1:13" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="6"/>
+      <c r="B19" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="103"/>
+      <c r="H19" s="104"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="55"/>
+      <c r="M19" s="52"/>
+    </row>
+    <row r="20" spans="1:13" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="61"/>
+      <c r="B20" s="105" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" s="99"/>
+      <c r="D20" s="99"/>
+      <c r="E20" s="99"/>
+      <c r="F20" s="99"/>
+      <c r="G20" s="99"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="92"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="52"/>
+      <c r="L20" s="55"/>
+      <c r="M20" s="52"/>
+    </row>
+    <row r="21" spans="1:13" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="61"/>
+      <c r="B21" s="98" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="99"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="99"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="55"/>
+      <c r="M21" s="52"/>
+    </row>
+    <row r="22" spans="1:13" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="61"/>
+      <c r="B22" s="98" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="99"/>
+      <c r="D22" s="99"/>
+      <c r="E22" s="99"/>
+      <c r="F22" s="99"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="100"/>
+      <c r="I22" s="92"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="52"/>
+      <c r="L22" s="55"/>
+      <c r="M22" s="52"/>
+    </row>
+    <row r="23" spans="1:13" s="1" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="61"/>
+      <c r="B23" s="56" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="88" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="58" t="s">
+      <c r="D23" s="88" t="s">
         <v>78</v>
       </c>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="53"/>
-    </row>
-    <row r="19" spans="1:12" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="54" t="s">
+      <c r="E23" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="F23" s="90" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" s="90" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="95" t="s">
+        <v>82</v>
+      </c>
+      <c r="I23" s="97"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="51"/>
+      <c r="L23" s="50"/>
+      <c r="M23" s="52"/>
+    </row>
+    <row r="24" spans="1:13" s="1" customFormat="1" ht="111.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="61"/>
+      <c r="B24" s="53" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="54"/>
-      <c r="D19" s="54"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="88"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="56"/>
-      <c r="J19" s="53"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="53"/>
-    </row>
-    <row r="20" spans="1:12" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="63"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="81"/>
-      <c r="E20" s="82"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="59"/>
-      <c r="I20" s="84"/>
-      <c r="J20" s="85"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="87"/>
-    </row>
-    <row r="21" spans="1:12" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="98" t="s">
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="85"/>
+      <c r="G24" s="89"/>
+      <c r="H24" s="96"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="91"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="55"/>
+      <c r="M24" s="52"/>
+    </row>
+    <row r="25" spans="1:13" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="61"/>
+      <c r="B25" s="77"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="79"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="57"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="82"/>
+      <c r="L25" s="83"/>
+      <c r="M25" s="84"/>
+    </row>
+    <row r="26" spans="1:13" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="6"/>
+      <c r="B26" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="91"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="91"/>
-      <c r="F21" s="91"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="59"/>
-      <c r="I21" s="60"/>
-      <c r="J21" s="61"/>
-      <c r="K21" s="60"/>
-      <c r="L21" s="62"/>
-    </row>
-    <row r="22" spans="1:12" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="6"/>
-      <c r="B22" s="98" t="s">
+      <c r="C26" s="99"/>
+      <c r="D26" s="99"/>
+      <c r="E26" s="99"/>
+      <c r="F26" s="99"/>
+      <c r="G26" s="99"/>
+      <c r="H26" s="108"/>
+      <c r="I26" s="57"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="59"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="60"/>
+    </row>
+    <row r="27" spans="1:13" s="1" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="6"/>
+      <c r="B27" s="114" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="91"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="59"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="61"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="62"/>
-    </row>
-    <row r="23" spans="1:12" s="1" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="6"/>
-      <c r="B23" s="98" t="s">
+      <c r="C27" s="99"/>
+      <c r="D27" s="99"/>
+      <c r="E27" s="99"/>
+      <c r="F27" s="99"/>
+      <c r="G27" s="99"/>
+      <c r="H27" s="108"/>
+      <c r="I27" s="57"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="60"/>
+    </row>
+    <row r="28" spans="1:13" s="1" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="6"/>
+      <c r="B28" s="114" t="s">
         <v>51</v>
       </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="59"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="61"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="62"/>
-    </row>
-    <row r="24" spans="1:12" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="6"/>
-      <c r="B24" s="98" t="s">
+      <c r="C28" s="99"/>
+      <c r="D28" s="99"/>
+      <c r="E28" s="99"/>
+      <c r="F28" s="99"/>
+      <c r="G28" s="99"/>
+      <c r="H28" s="108"/>
+      <c r="I28" s="57"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="59"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="60"/>
+    </row>
+    <row r="29" spans="1:13" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="6"/>
+      <c r="B29" s="114" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="59"/>
-      <c r="I24" s="60"/>
-      <c r="J24" s="61"/>
-      <c r="K24" s="60"/>
-      <c r="L24" s="62"/>
-    </row>
-    <row r="25" spans="1:12" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
-      <c r="B25" s="98" t="s">
+      <c r="C29" s="99"/>
+      <c r="D29" s="99"/>
+      <c r="E29" s="99"/>
+      <c r="F29" s="99"/>
+      <c r="G29" s="99"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="57"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="59"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="60"/>
+    </row>
+    <row r="30" spans="1:13" s="1" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="6"/>
+      <c r="B30" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="59"/>
-      <c r="I25" s="60"/>
-      <c r="J25" s="61"/>
-      <c r="K25" s="60"/>
-      <c r="L25" s="62"/>
-    </row>
-    <row r="26" spans="1:12" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="6"/>
-      <c r="B26" s="98" t="s">
+      <c r="C30" s="99"/>
+      <c r="D30" s="99"/>
+      <c r="E30" s="99"/>
+      <c r="F30" s="99"/>
+      <c r="G30" s="99"/>
+      <c r="H30" s="108"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="59"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="60"/>
+    </row>
+    <row r="31" spans="1:13" s="1" customFormat="1" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="6"/>
+      <c r="B31" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="91"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="92"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="41"/>
-      <c r="J26" s="21"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="22"/>
-    </row>
-    <row r="27" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="6"/>
-      <c r="B27" s="98" t="s">
+      <c r="C31" s="99"/>
+      <c r="D31" s="99"/>
+      <c r="E31" s="99"/>
+      <c r="F31" s="99"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="108"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="41"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="22"/>
+    </row>
+    <row r="32" spans="1:13" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="6"/>
+      <c r="B32" s="114" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="92"/>
-      <c r="H27" s="40"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="22"/>
-    </row>
-    <row r="28" spans="1:12" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="6"/>
-      <c r="B28" s="98" t="s">
+      <c r="C32" s="99"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="108"/>
+      <c r="I32" s="40"/>
+      <c r="J32" s="41"/>
+      <c r="K32" s="21"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="22"/>
+    </row>
+    <row r="33" spans="1:13" s="1" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="114" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="91"/>
-      <c r="D28" s="91"/>
-      <c r="E28" s="91"/>
-      <c r="F28" s="91"/>
-      <c r="G28" s="92"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="21"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="22"/>
-    </row>
-    <row r="29" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="6"/>
-      <c r="B29" s="42"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="43"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="19"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="15"/>
-    </row>
-    <row r="30" spans="1:12" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="6"/>
-      <c r="B30" s="29" t="s">
+      <c r="C33" s="99"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="108"/>
+      <c r="I33" s="40"/>
+      <c r="J33" s="41"/>
+      <c r="K33" s="21"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="6"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="43"/>
+      <c r="D34" s="43"/>
+      <c r="E34" s="43"/>
+      <c r="F34" s="43"/>
+      <c r="G34" s="43"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="6"/>
+      <c r="M34" s="15"/>
+    </row>
+    <row r="35" spans="1:13" s="1" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="6"/>
+      <c r="B35" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="26"/>
-      <c r="H30" s="19"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="24"/>
-    </row>
-    <row r="31" spans="1:12" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
-      <c r="B31" s="28" t="s">
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="24"/>
+    </row>
+    <row r="36" spans="1:13" s="1" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="6"/>
+      <c r="B36" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="16"/>
-      <c r="G31" s="26"/>
-      <c r="H31" s="19"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="15"/>
-    </row>
-    <row r="32" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="6"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
-      <c r="F32" s="16"/>
-      <c r="G32" s="26"/>
-      <c r="H32" s="19"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="15"/>
-    </row>
-    <row r="33" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="96" t="s">
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="6"/>
+      <c r="M36" s="15"/>
+    </row>
+    <row r="37" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="6"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="16"/>
+      <c r="G37" s="16"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="15"/>
+    </row>
+    <row r="38" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="6"/>
+      <c r="B38" s="112" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="91"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="19"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="15"/>
-    </row>
-    <row r="34" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="6"/>
-      <c r="B34" s="90" t="s">
+      <c r="C38" s="99"/>
+      <c r="D38" s="99"/>
+      <c r="E38" s="99"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="6"/>
+      <c r="M38" s="15"/>
+    </row>
+    <row r="39" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="6"/>
+      <c r="B39" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="C34" s="91"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="92"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="15"/>
-    </row>
-    <row r="35" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="6"/>
-      <c r="B35" s="90" t="s">
+      <c r="C39" s="99"/>
+      <c r="D39" s="99"/>
+      <c r="E39" s="99"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="6"/>
+      <c r="B40" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="C35" s="91"/>
-      <c r="D35" s="91"/>
-      <c r="E35" s="91"/>
-      <c r="F35" s="91"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="15"/>
-    </row>
-    <row r="36" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="63"/>
-      <c r="B36" s="65"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="75"/>
-      <c r="K36" s="63"/>
-      <c r="L36" s="76"/>
-    </row>
-    <row r="37" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
-      <c r="B37" s="93"/>
-      <c r="C37" s="94"/>
-      <c r="D37" s="94"/>
-      <c r="E37" s="94"/>
-      <c r="F37" s="94"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="19"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="15"/>
-    </row>
-    <row r="38" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="6"/>
-      <c r="B38" s="96" t="s">
+      <c r="C40" s="99"/>
+      <c r="D40" s="99"/>
+      <c r="E40" s="99"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="15"/>
+    </row>
+    <row r="41" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="61"/>
+      <c r="B41" s="63"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="62"/>
+      <c r="J41" s="61"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="61"/>
+      <c r="M41" s="74"/>
+    </row>
+    <row r="42" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="6"/>
+      <c r="B42" s="109"/>
+      <c r="C42" s="110"/>
+      <c r="D42" s="110"/>
+      <c r="E42" s="110"/>
+      <c r="F42" s="110"/>
+      <c r="G42" s="106"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="6"/>
+      <c r="M42" s="15"/>
+    </row>
+    <row r="43" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="6"/>
+      <c r="B43" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="91"/>
-      <c r="D38" s="91"/>
-      <c r="E38" s="91"/>
-      <c r="F38" s="91"/>
-      <c r="G38" s="92"/>
-      <c r="H38" s="19"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="15"/>
-    </row>
-    <row r="39" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="6"/>
-      <c r="B39" s="97" t="s">
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="108"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="6"/>
+      <c r="M43" s="15"/>
+    </row>
+    <row r="44" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="6"/>
+      <c r="B44" s="113" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="94"/>
-      <c r="D39" s="94"/>
-      <c r="E39" s="94"/>
-      <c r="F39" s="94"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="15"/>
-    </row>
-    <row r="40" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="97" t="s">
+      <c r="C44" s="110"/>
+      <c r="D44" s="110"/>
+      <c r="E44" s="110"/>
+      <c r="F44" s="110"/>
+      <c r="G44" s="106"/>
+      <c r="H44" s="111"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="6"/>
+      <c r="M44" s="15"/>
+    </row>
+    <row r="45" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="6"/>
+      <c r="B45" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="94"/>
-      <c r="D40" s="94"/>
-      <c r="E40" s="94"/>
-      <c r="F40" s="94"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="6"/>
-      <c r="L40" s="15"/>
-    </row>
-    <row r="41" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="6"/>
-      <c r="B41" s="112" t="s">
+      <c r="C45" s="110"/>
+      <c r="D45" s="110"/>
+      <c r="E45" s="110"/>
+      <c r="F45" s="110"/>
+      <c r="G45" s="106"/>
+      <c r="H45" s="111"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="6"/>
+      <c r="M45" s="15"/>
+    </row>
+    <row r="46" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="6"/>
+      <c r="B46" s="133" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="91"/>
-      <c r="D41" s="91"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="91"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="6"/>
-      <c r="L41" s="15"/>
-    </row>
-    <row r="42" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="6"/>
-      <c r="B42" s="112" t="s">
+      <c r="C46" s="99"/>
+      <c r="D46" s="99"/>
+      <c r="E46" s="99"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="108"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="6"/>
+      <c r="M46" s="15"/>
+    </row>
+    <row r="47" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="6"/>
+      <c r="B47" s="133" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="91"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="6"/>
-      <c r="L42" s="15"/>
-    </row>
-    <row r="43" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="6"/>
-      <c r="B43" s="113" t="s">
+      <c r="C47" s="99"/>
+      <c r="D47" s="99"/>
+      <c r="E47" s="99"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="108"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="6"/>
+      <c r="M47" s="15"/>
+    </row>
+    <row r="48" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="6"/>
+      <c r="B48" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="92"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="15"/>
-    </row>
-    <row r="44" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="6"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="91"/>
-      <c r="G44" s="92"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="15"/>
-    </row>
-    <row r="45" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="6"/>
-      <c r="B45" s="96" t="s">
+      <c r="C48" s="99"/>
+      <c r="D48" s="99"/>
+      <c r="E48" s="99"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="108"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="6"/>
+      <c r="M48" s="15"/>
+    </row>
+    <row r="49" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="6"/>
+      <c r="B49" s="135"/>
+      <c r="C49" s="99"/>
+      <c r="D49" s="99"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="108"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="6"/>
+      <c r="M49" s="15"/>
+    </row>
+    <row r="50" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="6"/>
+      <c r="B50" s="112" t="s">
         <v>26</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="91"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="6"/>
-      <c r="L45" s="15"/>
-    </row>
-    <row r="46" spans="1:12" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="6"/>
-      <c r="B46" s="109" t="s">
+      <c r="C50" s="99"/>
+      <c r="D50" s="99"/>
+      <c r="E50" s="99"/>
+      <c r="F50" s="99"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="6"/>
+      <c r="M50" s="15"/>
+    </row>
+    <row r="51" spans="1:13" s="1" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="6"/>
+      <c r="B51" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="110"/>
-      <c r="D46" s="110"/>
-      <c r="E46" s="110"/>
-      <c r="F46" s="110"/>
-      <c r="G46" s="111"/>
-      <c r="H46" s="19"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="15"/>
-    </row>
-    <row r="47" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="6"/>
-      <c r="B47" s="90" t="s">
+      <c r="C51" s="131"/>
+      <c r="D51" s="131"/>
+      <c r="E51" s="131"/>
+      <c r="F51" s="131"/>
+      <c r="G51" s="131"/>
+      <c r="H51" s="132"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="15"/>
+    </row>
+    <row r="52" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="6"/>
+      <c r="B52" s="107" t="s">
         <v>59</v>
       </c>
-      <c r="C47" s="91"/>
-      <c r="D47" s="91"/>
-      <c r="E47" s="91"/>
-      <c r="F47" s="91"/>
-      <c r="G47" s="25"/>
-      <c r="H47" s="19"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="15"/>
-    </row>
-    <row r="48" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="6"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="26"/>
-      <c r="H48" s="19"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="15"/>
-    </row>
-    <row r="49" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="6"/>
-      <c r="B49" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="26"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="15"/>
-    </row>
-    <row r="50" spans="1:12" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="6"/>
-      <c r="B50" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C50" s="16"/>
-      <c r="D50" s="16"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="16"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="19"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="15"/>
-    </row>
-    <row r="51" spans="1:12" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="6"/>
-      <c r="B51" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="16"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="19"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="15"/>
-    </row>
-    <row r="52" spans="1:12" s="1" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="6"/>
-      <c r="B52" s="118" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="91"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="91"/>
-      <c r="F52" s="91"/>
-      <c r="G52" s="92"/>
-      <c r="H52" s="19"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="15"/>
-    </row>
-    <row r="53" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="99"/>
+      <c r="D52" s="99"/>
+      <c r="E52" s="99"/>
+      <c r="F52" s="99"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="19"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="15"/>
+    </row>
+    <row r="53" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6"/>
       <c r="B53" s="29"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
       <c r="F53" s="16"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="19"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="15"/>
-    </row>
-    <row r="54" spans="1:12" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G53" s="16"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="19"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="15"/>
+    </row>
+    <row r="54" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6"/>
       <c r="B54" s="27" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
       <c r="F54" s="16"/>
-      <c r="G54" s="26"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="15"/>
-    </row>
-    <row r="55" spans="1:12" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G54" s="16"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="15"/>
+    </row>
+    <row r="55" spans="1:13" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6"/>
       <c r="B55" s="28" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
       <c r="F55" s="16"/>
-      <c r="G55" s="26"/>
-      <c r="H55" s="19"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="15"/>
-    </row>
-    <row r="56" spans="1:12" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G55" s="16"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="19"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="15"/>
+    </row>
+    <row r="56" spans="1:13" s="1" customFormat="1" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6"/>
       <c r="B56" s="28" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
       <c r="F56" s="16"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="19"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="15"/>
-    </row>
-    <row r="57" spans="1:12" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G56" s="16"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="19"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="15"/>
+    </row>
+    <row r="57" spans="1:13" s="1" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6"/>
-      <c r="B57" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="26"/>
-      <c r="H57" s="19"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="15"/>
-    </row>
-    <row r="58" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B57" s="145" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="99"/>
+      <c r="D57" s="99"/>
+      <c r="E57" s="99"/>
+      <c r="F57" s="99"/>
+      <c r="G57" s="99"/>
+      <c r="H57" s="108"/>
+      <c r="I57" s="19"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="15"/>
+    </row>
+    <row r="58" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6"/>
-      <c r="B58" s="23"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
       <c r="F58" s="16"/>
-      <c r="G58" s="26"/>
-      <c r="H58" s="19"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="6"/>
-      <c r="L58" s="15"/>
-    </row>
-    <row r="59" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G58" s="16"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="19"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="15"/>
+    </row>
+    <row r="59" spans="1:13" s="1" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6"/>
-      <c r="B59" s="30" t="s">
-        <v>36</v>
+      <c r="B59" s="27" t="s">
+        <v>32</v>
       </c>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
       <c r="E59" s="16"/>
       <c r="F59" s="16"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="19"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="15"/>
-    </row>
-    <row r="60" spans="1:12" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G59" s="16"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="19"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="15"/>
+    </row>
+    <row r="60" spans="1:13" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>
-      <c r="B60" s="6" t="s">
-        <v>60</v>
+      <c r="B60" s="28" t="s">
+        <v>33</v>
       </c>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
       <c r="E60" s="16"/>
       <c r="F60" s="16"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="19"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="15"/>
-    </row>
-    <row r="61" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G60" s="16"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="19"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="15"/>
+    </row>
+    <row r="61" spans="1:13" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6"/>
-      <c r="B61" s="23"/>
+      <c r="B61" s="28" t="s">
+        <v>34</v>
+      </c>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
       <c r="E61" s="16"/>
       <c r="F61" s="16"/>
-      <c r="G61" s="26"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="15"/>
-    </row>
-    <row r="62" spans="1:12" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G61" s="16"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="15"/>
+    </row>
+    <row r="62" spans="1:13" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6"/>
-      <c r="B62" s="96" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="91"/>
-      <c r="D62" s="91"/>
-      <c r="E62" s="91"/>
+      <c r="B62" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="16"/>
       <c r="F62" s="16"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="19"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="15"/>
-    </row>
-    <row r="63" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G62" s="16"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="6"/>
+      <c r="M62" s="15"/>
+    </row>
+    <row r="63" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
+      <c r="B63" s="23"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
       <c r="E63" s="16"/>
       <c r="F63" s="16"/>
-      <c r="G63" s="17"/>
-      <c r="H63" s="18"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="15"/>
-    </row>
-    <row r="64" spans="1:12" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="8"/>
-      <c r="B64" s="119"/>
-      <c r="C64" s="106"/>
-      <c r="D64" s="106"/>
-      <c r="E64" s="106"/>
-      <c r="F64" s="106"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="46"/>
-      <c r="I64" s="8"/>
-      <c r="J64" s="47" t="s">
+      <c r="G63" s="16"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="19"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="6"/>
+      <c r="M63" s="15"/>
+    </row>
+    <row r="64" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="6"/>
+      <c r="B64" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="16"/>
+      <c r="D64" s="16"/>
+      <c r="E64" s="16"/>
+      <c r="F64" s="16"/>
+      <c r="G64" s="16"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="19"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="6"/>
+      <c r="M64" s="15"/>
+    </row>
+    <row r="65" spans="1:13" s="1" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="6"/>
+      <c r="B65" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="16"/>
+      <c r="F65" s="16"/>
+      <c r="G65" s="16"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="19"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="15"/>
+    </row>
+    <row r="66" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="6"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+      <c r="G66" s="16"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="19"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="15"/>
+    </row>
+    <row r="67" spans="1:13" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="6"/>
+      <c r="B67" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="99"/>
+      <c r="D67" s="99"/>
+      <c r="E67" s="99"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="26"/>
+      <c r="I67" s="19"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="14"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="15"/>
+    </row>
+    <row r="68" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+      <c r="G68" s="16"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="18"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="14"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="15"/>
+    </row>
+    <row r="69" spans="1:13" s="1" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="8"/>
+      <c r="B69" s="146"/>
+      <c r="C69" s="122"/>
+      <c r="D69" s="122"/>
+      <c r="E69" s="122"/>
+      <c r="F69" s="122"/>
+      <c r="G69" s="87"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="46"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="47" t="s">
         <v>37</v>
       </c>
-      <c r="K64" s="48" t="s">
+      <c r="L69" s="48" t="s">
         <v>38</v>
       </c>
-      <c r="L64" s="49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="31" t="s">
+      <c r="M69" s="49" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="1" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B65" s="120" t="str">
+      <c r="B70" s="147" t="str">
         <f>B13</f>
         <v>{{project_title}}</v>
       </c>
-      <c r="C65" s="121"/>
-      <c r="D65" s="121"/>
-      <c r="E65" s="121"/>
-      <c r="F65" s="121"/>
-      <c r="G65" s="121"/>
-      <c r="H65" s="121"/>
-      <c r="I65" s="121"/>
-      <c r="J65" s="121"/>
-      <c r="K65" s="121"/>
-      <c r="L65" s="122"/>
-    </row>
-    <row r="66" spans="1:12" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2"/>
-      <c r="B66" s="99" t="s">
+      <c r="C70" s="148"/>
+      <c r="D70" s="148"/>
+      <c r="E70" s="148"/>
+      <c r="F70" s="148"/>
+      <c r="G70" s="148"/>
+      <c r="H70" s="148"/>
+      <c r="I70" s="148"/>
+      <c r="J70" s="148"/>
+      <c r="K70" s="148"/>
+      <c r="L70" s="148"/>
+      <c r="M70" s="149"/>
+    </row>
+    <row r="71" spans="1:13" s="1" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2"/>
+      <c r="B71" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="C66" s="100"/>
-      <c r="D66" s="100"/>
-      <c r="E66" s="100"/>
-      <c r="F66" s="100"/>
-      <c r="G66" s="101"/>
-      <c r="H66" s="99" t="s">
+      <c r="C71" s="116"/>
+      <c r="D71" s="116"/>
+      <c r="E71" s="116"/>
+      <c r="F71" s="116"/>
+      <c r="G71" s="116"/>
+      <c r="H71" s="117"/>
+      <c r="I71" s="115" t="s">
         <v>41</v>
       </c>
-      <c r="I66" s="100"/>
-      <c r="J66" s="100"/>
-      <c r="K66" s="100"/>
-      <c r="L66" s="101"/>
-    </row>
-    <row r="67" spans="1:12" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="6"/>
-      <c r="B67" s="102"/>
-      <c r="C67" s="103"/>
-      <c r="D67" s="103"/>
-      <c r="E67" s="103"/>
-      <c r="F67" s="103"/>
-      <c r="G67" s="104"/>
-      <c r="H67" s="108"/>
-      <c r="I67" s="103"/>
-      <c r="J67" s="103"/>
-      <c r="K67" s="103"/>
-      <c r="L67" s="104"/>
-    </row>
-    <row r="68" spans="1:12" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="74" t="s">
+      <c r="J71" s="139"/>
+      <c r="K71" s="139"/>
+      <c r="L71" s="139"/>
+      <c r="M71" s="140"/>
+    </row>
+    <row r="72" spans="1:13" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="6"/>
+      <c r="B72" s="118"/>
+      <c r="C72" s="119"/>
+      <c r="D72" s="119"/>
+      <c r="E72" s="119"/>
+      <c r="F72" s="119"/>
+      <c r="G72" s="119"/>
+      <c r="H72" s="120"/>
+      <c r="I72" s="124"/>
+      <c r="J72" s="125"/>
+      <c r="K72" s="125"/>
+      <c r="L72" s="125"/>
+      <c r="M72" s="126"/>
+    </row>
+    <row r="73" spans="1:13" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="B68" s="105"/>
-      <c r="C68" s="106"/>
-      <c r="D68" s="106"/>
-      <c r="E68" s="106"/>
-      <c r="F68" s="106"/>
-      <c r="G68" s="107"/>
-      <c r="H68" s="105"/>
-      <c r="I68" s="106"/>
-      <c r="J68" s="106"/>
-      <c r="K68" s="106"/>
-      <c r="L68" s="107"/>
-    </row>
-    <row r="69" spans="1:12" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="32" t="s">
+      <c r="B73" s="121"/>
+      <c r="C73" s="122"/>
+      <c r="D73" s="122"/>
+      <c r="E73" s="122"/>
+      <c r="F73" s="122"/>
+      <c r="G73" s="122"/>
+      <c r="H73" s="123"/>
+      <c r="I73" s="127"/>
+      <c r="J73" s="128"/>
+      <c r="K73" s="128"/>
+      <c r="L73" s="128"/>
+      <c r="M73" s="129"/>
+    </row>
+    <row r="74" spans="1:13" s="1" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="32" t="s">
         <v>43</v>
       </c>
-      <c r="B69" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="C69" s="142"/>
-      <c r="D69" s="142"/>
-      <c r="E69" s="142"/>
-      <c r="F69" s="142"/>
-      <c r="G69" s="143"/>
-      <c r="H69" s="99" t="s">
+      <c r="B74" s="136" t="s">
+        <v>67</v>
+      </c>
+      <c r="C74" s="137"/>
+      <c r="D74" s="137"/>
+      <c r="E74" s="137"/>
+      <c r="F74" s="137"/>
+      <c r="G74" s="137"/>
+      <c r="H74" s="138"/>
+      <c r="I74" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="I69" s="100"/>
-      <c r="J69" s="100"/>
-      <c r="K69" s="100"/>
-      <c r="L69" s="101"/>
-    </row>
-    <row r="70" spans="1:12" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="33" t="s">
+      <c r="J74" s="139"/>
+      <c r="K74" s="139"/>
+      <c r="L74" s="139"/>
+      <c r="M74" s="140"/>
+    </row>
+    <row r="75" spans="1:13" s="1" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="B70" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="100"/>
-      <c r="D70" s="100"/>
-      <c r="E70" s="100"/>
-      <c r="F70" s="100"/>
-      <c r="G70" s="101"/>
-      <c r="H70" s="117" t="s">
+      <c r="B75" s="141" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="116"/>
+      <c r="D75" s="116"/>
+      <c r="E75" s="116"/>
+      <c r="F75" s="116"/>
+      <c r="G75" s="116"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="I70" s="100"/>
-      <c r="J70" s="100"/>
-      <c r="K70" s="100"/>
-      <c r="L70" s="101"/>
-    </row>
-    <row r="71" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="J75" s="143"/>
+      <c r="K75" s="143"/>
+      <c r="L75" s="143"/>
+      <c r="M75" s="144"/>
+    </row>
+    <row r="76" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3296,56 +3660,66 @@
     <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="B13:G14"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A7:L7"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="B69:G69"/>
-    <mergeCell ref="H69:L69"/>
-    <mergeCell ref="B70:G70"/>
-    <mergeCell ref="H70:L70"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B62:E62"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B65:L65"/>
-    <mergeCell ref="H66:L66"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="B41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="B43:G43"/>
-    <mergeCell ref="B44:G44"/>
-    <mergeCell ref="B45:F45"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="B67:G68"/>
-    <mergeCell ref="H67:L68"/>
-    <mergeCell ref="B46:G46"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B37:G37"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B39:G39"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
+  <mergeCells count="53">
+    <mergeCell ref="B13:H14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="B16:H16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="A7:M7"/>
+    <mergeCell ref="A8:M8"/>
+    <mergeCell ref="B12:H12"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="B74:H74"/>
+    <mergeCell ref="I74:M74"/>
+    <mergeCell ref="B75:H75"/>
+    <mergeCell ref="I75:M75"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B57:H57"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B70:M70"/>
+    <mergeCell ref="I71:M71"/>
+    <mergeCell ref="B45:H45"/>
+    <mergeCell ref="B46:H46"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="B48:H48"/>
+    <mergeCell ref="B49:H49"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B71:H71"/>
+    <mergeCell ref="B72:H73"/>
+    <mergeCell ref="I72:M73"/>
+    <mergeCell ref="B51:H51"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B42:H42"/>
+    <mergeCell ref="B43:H43"/>
+    <mergeCell ref="B44:H44"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="B38:H38"/>
+    <mergeCell ref="B39:H39"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="B21:H21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="37" fitToHeight="0" orientation="portrait" r:id="rId1"/>
